--- a/output/pdf_financials_xlsx/RAIN.xlsx
+++ b/output/pdf_financials_xlsx/RAIN.xlsx
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.023879</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.056543</v>
       </c>
     </row>
     <row r="35">
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.354856</v>
+        <v>0.378735</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.07341200000000001</v>
+        <v>0.129955</v>
       </c>
     </row>
     <row r="37">
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.026379</v>
+        <v>0.0025</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.056543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/RAIN.xlsx
+++ b/output/pdf_financials_xlsx/RAIN.xlsx
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-0.255</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.099523</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.147526</v>
       </c>
     </row>
     <row r="116">
@@ -3164,7 +3164,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>-0.255</v>
       </c>
@@ -3190,7 +3194,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>0.099523</v>
       </c>
@@ -3266,7 +3274,11 @@
           <t>Proceeds received from private placement</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>1.361952</v>
       </c>
